--- a/intercom_end_point.xlsx
+++ b/intercom_end_point.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brad.parker/projects/SystemSurveyor/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA408656-A1B7-D24D-8087-4636B5514BA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E29A30CF-2AD7-7748-92B2-C65E16FACE55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1770" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1822" uniqueCount="207">
   <si>
     <t>Export date: Jun 29, 2026</t>
   </si>
@@ -555,6 +555,105 @@
   </si>
   <si>
     <t>TD63</t>
+  </si>
+  <si>
+    <t>TK74 - Touchscreen Intercom</t>
+  </si>
+  <si>
+    <t>TK74</t>
+  </si>
+  <si>
+    <t>Verkada TK74 Intercoms Page</t>
+  </si>
+  <si>
+    <t>https://www.verkada.com/intercom/tk74/</t>
+  </si>
+  <si>
+    <t>TS74 Product Datasheet</t>
+  </si>
+  <si>
+    <t>https://docs.verkada.com/docs/tk74-touchscreen-intercom-datasheet.pdf</t>
+  </si>
+  <si>
+    <t>TK74 Side Angle Mount</t>
+  </si>
+  <si>
+    <t>ACC-INT-TK-ANGLE</t>
+  </si>
+  <si>
+    <t>TK74 Conduit Surface Mount</t>
+  </si>
+  <si>
+    <t>ACC-INT-TK-COND</t>
+  </si>
+  <si>
+    <t>ACC-INT-TK-UP</t>
+  </si>
+  <si>
+    <t>ACC-INT-TK-FLUSH</t>
+  </si>
+  <si>
+    <t>ACC-AF-MUL-2</t>
+  </si>
+  <si>
+    <t>TK74 Up Angle Mount</t>
+  </si>
+  <si>
+    <t>TK74 Flush Mount</t>
+  </si>
+  <si>
+    <t>AF64 Mullion Mount - 2</t>
+  </si>
+  <si>
+    <t>Accessory27</t>
+  </si>
+  <si>
+    <t>Accessory28</t>
+  </si>
+  <si>
+    <t>Accessory29</t>
+  </si>
+  <si>
+    <t>Accessory30</t>
+  </si>
+  <si>
+    <t>Accessory31</t>
+  </si>
+  <si>
+    <t>1-Year Intercom Tenant License (for 10 tenants), Capacity Increase</t>
+  </si>
+  <si>
+    <t>3-Year Intercom Tenant License (for 10 tenants), Capacity Increase</t>
+  </si>
+  <si>
+    <t>5-Year Intercom Tenant License (for 10 tenants), Capacity Increase</t>
+  </si>
+  <si>
+    <t>10-Year Intercom Tenant License (for 10 tenants), Capacity Increase</t>
+  </si>
+  <si>
+    <t>LIC-ITT-1Y-CAP</t>
+  </si>
+  <si>
+    <t>LIC-ITT-3Y-CAP</t>
+  </si>
+  <si>
+    <t>LIC-ITT-5Y-CAP</t>
+  </si>
+  <si>
+    <t>LIC-ITT-10Y-CAP</t>
+  </si>
+  <si>
+    <t>Accessory32</t>
+  </si>
+  <si>
+    <t>Accessory33</t>
+  </si>
+  <si>
+    <t>Accessory34</t>
+  </si>
+  <si>
+    <t>Accessory35</t>
   </si>
 </sst>
 </file>
@@ -2127,15 +2226,17 @@
         <v>7</v>
       </c>
       <c r="H3" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="K3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="3"/>
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
@@ -2647,15 +2748,17 @@
         <v>7</v>
       </c>
       <c r="H4" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="I4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="J4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="K4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="K4" s="5"/>
       <c r="L4" s="5"/>
       <c r="M4" s="5"/>
       <c r="N4" s="5"/>
@@ -4679,7 +4782,9 @@
       <c r="J6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="K6" s="5"/>
+      <c r="K6" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="L6" s="5"/>
       <c r="M6" s="5"/>
       <c r="N6" s="5"/>
@@ -5197,7 +5302,9 @@
       <c r="J7" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="K7" s="5"/>
+      <c r="K7" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="L7" s="5"/>
       <c r="M7" s="5"/>
       <c r="N7" s="5"/>
@@ -5707,15 +5814,17 @@
         <v>173</v>
       </c>
       <c r="H8" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="I8" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="J8" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="J8" s="5" t="s">
+      <c r="K8" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="K8" s="5"/>
       <c r="L8" s="5"/>
       <c r="M8" s="5"/>
       <c r="N8" s="5"/>
@@ -7731,7 +7840,7 @@
         <v>1999</v>
       </c>
       <c r="H10" s="5">
-        <v>1099</v>
+        <v>3999</v>
       </c>
       <c r="I10" s="5">
         <v>1099</v>
@@ -7739,7 +7848,9 @@
       <c r="J10" s="5">
         <v>1099</v>
       </c>
-      <c r="K10" s="5"/>
+      <c r="K10" s="5">
+        <v>1099</v>
+      </c>
       <c r="L10" s="5"/>
       <c r="M10" s="5"/>
       <c r="N10" s="5"/>
@@ -11791,7 +11902,9 @@
       <c r="J16" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="K16" s="5"/>
+      <c r="K16" s="5" t="s">
+        <v>35</v>
+      </c>
       <c r="L16" s="5"/>
       <c r="M16" s="5"/>
       <c r="N16" s="5"/>
@@ -12309,7 +12422,9 @@
       <c r="J17" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="K17" s="5"/>
+      <c r="K17" s="5" t="s">
+        <v>39</v>
+      </c>
       <c r="L17" s="5"/>
       <c r="M17" s="5"/>
       <c r="N17" s="5"/>
@@ -13333,7 +13448,9 @@
       <c r="J19" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="K19" s="5"/>
+      <c r="K19" s="5" t="s">
+        <v>42</v>
+      </c>
       <c r="L19" s="5"/>
       <c r="M19" s="5"/>
       <c r="N19" s="5"/>
@@ -14869,7 +14986,9 @@
       <c r="J22" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="K22" s="7"/>
+      <c r="K22" s="7" t="s">
+        <v>42</v>
+      </c>
       <c r="L22" s="7"/>
       <c r="M22" s="7"/>
       <c r="N22" s="7"/>
@@ -15893,7 +16012,9 @@
       <c r="J24" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="K24" s="7"/>
+      <c r="K24" s="7" t="s">
+        <v>42</v>
+      </c>
       <c r="L24" s="7"/>
       <c r="M24" s="7"/>
       <c r="N24" s="7"/>
@@ -20971,7 +21092,7 @@
         <v>60</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>61</v>
+        <v>176</v>
       </c>
       <c r="I34" s="10" t="s">
         <v>61</v>
@@ -20979,7 +21100,9 @@
       <c r="J34" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="K34" s="10"/>
+      <c r="K34" s="10" t="s">
+        <v>61</v>
+      </c>
       <c r="L34" s="10"/>
       <c r="M34" s="10"/>
       <c r="N34" s="10"/>
@@ -21489,7 +21612,7 @@
         <v>63</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>64</v>
+        <v>177</v>
       </c>
       <c r="I35" s="10" t="s">
         <v>64</v>
@@ -21497,7 +21620,9 @@
       <c r="J35" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="K35" s="10"/>
+      <c r="K35" s="10" t="s">
+        <v>64</v>
+      </c>
       <c r="L35" s="10"/>
       <c r="M35" s="10"/>
       <c r="N35" s="10"/>
@@ -22007,7 +22132,7 @@
         <v>68</v>
       </c>
       <c r="H36" s="10" t="s">
-        <v>69</v>
+        <v>178</v>
       </c>
       <c r="I36" s="10" t="s">
         <v>69</v>
@@ -22015,7 +22140,9 @@
       <c r="J36" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="K36" s="10"/>
+      <c r="K36" s="10" t="s">
+        <v>69</v>
+      </c>
       <c r="L36" s="10"/>
       <c r="M36" s="10"/>
       <c r="N36" s="10"/>
@@ -22525,7 +22652,7 @@
         <v>73</v>
       </c>
       <c r="H37" s="11" t="s">
-        <v>74</v>
+        <v>179</v>
       </c>
       <c r="I37" s="11" t="s">
         <v>74</v>
@@ -22533,7 +22660,9 @@
       <c r="J37" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="K37" s="11"/>
+      <c r="K37" s="11" t="s">
+        <v>74</v>
+      </c>
       <c r="L37" s="11"/>
       <c r="M37" s="11"/>
       <c r="N37" s="11"/>
@@ -23053,7 +23182,9 @@
       <c r="J38" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="K38" s="10"/>
+      <c r="K38" s="10" t="s">
+        <v>76</v>
+      </c>
       <c r="L38" s="10"/>
       <c r="M38" s="10"/>
       <c r="N38" s="10"/>
@@ -23563,7 +23694,7 @@
         <v>78</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I39" s="10" t="s">
         <v>79</v>
@@ -23571,7 +23702,9 @@
       <c r="J39" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="K39" s="10"/>
+      <c r="K39" s="10" t="s">
+        <v>79</v>
+      </c>
       <c r="L39" s="10"/>
       <c r="M39" s="10"/>
       <c r="N39" s="10"/>
@@ -28182,7 +28315,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -28733,6 +28866,186 @@
         <v>0</v>
       </c>
     </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>190</v>
+      </c>
+      <c r="B28" t="s">
+        <v>180</v>
+      </c>
+      <c r="C28" t="s">
+        <v>18</v>
+      </c>
+      <c r="D28" t="s">
+        <v>181</v>
+      </c>
+      <c r="E28">
+        <v>399</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>191</v>
+      </c>
+      <c r="B29" t="s">
+        <v>182</v>
+      </c>
+      <c r="C29" t="s">
+        <v>18</v>
+      </c>
+      <c r="D29" t="s">
+        <v>183</v>
+      </c>
+      <c r="E29">
+        <v>399</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>192</v>
+      </c>
+      <c r="B30" t="s">
+        <v>187</v>
+      </c>
+      <c r="C30" t="s">
+        <v>18</v>
+      </c>
+      <c r="D30" t="s">
+        <v>184</v>
+      </c>
+      <c r="E30">
+        <v>399</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>193</v>
+      </c>
+      <c r="B31" t="s">
+        <v>188</v>
+      </c>
+      <c r="C31" t="s">
+        <v>18</v>
+      </c>
+      <c r="D31" t="s">
+        <v>185</v>
+      </c>
+      <c r="E31">
+        <v>399</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>194</v>
+      </c>
+      <c r="B32" t="s">
+        <v>189</v>
+      </c>
+      <c r="C32" t="s">
+        <v>18</v>
+      </c>
+      <c r="D32" t="s">
+        <v>186</v>
+      </c>
+      <c r="E32">
+        <v>399</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>203</v>
+      </c>
+      <c r="B33" t="s">
+        <v>195</v>
+      </c>
+      <c r="C33" t="s">
+        <v>18</v>
+      </c>
+      <c r="D33" t="s">
+        <v>199</v>
+      </c>
+      <c r="E33">
+        <v>399</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>204</v>
+      </c>
+      <c r="B34" t="s">
+        <v>196</v>
+      </c>
+      <c r="C34" t="s">
+        <v>18</v>
+      </c>
+      <c r="D34" t="s">
+        <v>200</v>
+      </c>
+      <c r="E34">
+        <v>1199</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>205</v>
+      </c>
+      <c r="B35" t="s">
+        <v>197</v>
+      </c>
+      <c r="C35" t="s">
+        <v>18</v>
+      </c>
+      <c r="D35" t="s">
+        <v>201</v>
+      </c>
+      <c r="E35">
+        <v>1999</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>206</v>
+      </c>
+      <c r="B36" t="s">
+        <v>198</v>
+      </c>
+      <c r="C36" t="s">
+        <v>18</v>
+      </c>
+      <c r="D36" t="s">
+        <v>202</v>
+      </c>
+      <c r="E36">
+        <v>3999</v>
+      </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
